--- a/Road Map.xlsx
+++ b/Road Map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2081126\aem_practice\JS-and-React-Js\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64672F42-BC08-4F48-A0C9-095AF13D11AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D2CBE6D-61E4-4AF2-B0C2-6A0C1D84B96E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -981,16 +981,16 @@
       <c r="A4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="4" t="s">
         <v>22</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="4" t="s">
         <v>24</v>
       </c>
       <c r="F4" s="2" t="s">
@@ -1007,10 +1007,10 @@
       <c r="B5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E5" s="2" t="s">
@@ -1027,16 +1027,16 @@
       <c r="A6" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="4" t="s">
         <v>36</v>
       </c>
       <c r="F6" s="2" t="s">
@@ -1053,13 +1053,13 @@
       <c r="B7" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="4" t="s">
         <v>42</v>
       </c>
       <c r="F7" s="2" t="s">
@@ -1513,7 +1513,7 @@
       <c r="B27" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="4" t="s">
         <v>154</v>
       </c>
       <c r="D27" s="2" t="s">
